--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R241163df5bcd4e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra18aa2f648794483"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra18aa2f648794483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80915e0dc2274c8f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80915e0dc2274c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2a30c1193814039"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2a30c1193814039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c026346237849bb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c026346237849bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd83981d9c6914b66"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd83981d9c6914b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fe69c5851c44704"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6fe69c5851c44704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a6ef4d08ec44721"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4a6ef4d08ec44721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b549ef4f7ec4849"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b549ef4f7ec4849"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78df50eb57a24cb4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78df50eb57a24cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5de874a4e9cf4cfe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5de874a4e9cf4cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdffb4aa6c7c74157"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdffb4aa6c7c74157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8efca81f522e4623"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8efca81f522e4623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46862a3459cd4d53"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46862a3459cd4d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0e8d615d20304350"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupLandscapeWithMargins/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0e8d615d20304350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R16d3bafe978742dc"/>
   </x:sheets>
 </x:workbook>
 </file>
